--- a/results/Results.xlsx
+++ b/results/Results.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johannes/Documents/GitHub/differentiable-er/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E6DBB13-4D75-314F-AAE7-883C946CD37E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9CF6C4-7748-E84A-975D-9943CB36BAC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13740" yWindow="7760" windowWidth="28040" windowHeight="17440" activeTab="1" xr2:uid="{A7042B4A-C49B-F340-AB38-2066DB0192FA}"/>
+    <workbookView xWindow="21080" yWindow="9280" windowWidth="23960" windowHeight="17440" activeTab="2" xr2:uid="{A7042B4A-C49B-F340-AB38-2066DB0192FA}"/>
   </bookViews>
   <sheets>
     <sheet name="NAP" sheetId="1" r:id="rId1"/>
-    <sheet name="NAP detail" sheetId="2" r:id="rId2"/>
-    <sheet name="suffix" sheetId="3" r:id="rId3"/>
+    <sheet name="NAP new" sheetId="4" r:id="rId2"/>
+    <sheet name="Suffix new" sheetId="5" r:id="rId3"/>
+    <sheet name="NAP detail" sheetId="2" r:id="rId4"/>
+    <sheet name="suffix" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="22">
   <si>
     <t>F1</t>
   </si>
@@ -95,6 +97,15 @@
   </si>
   <si>
     <t>Baseline</t>
+  </si>
+  <si>
+    <t>Rank loss</t>
+  </si>
+  <si>
+    <t>Precision</t>
+  </si>
+  <si>
+    <t>Base</t>
   </si>
 </sst>
 </file>
@@ -377,7 +388,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -395,6 +406,41 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -404,36 +450,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -776,14 +808,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17" t="s">
+      <c r="D2" s="52"/>
+      <c r="E2" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="17"/>
+      <c r="F2" s="52"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
@@ -914,6 +946,342 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{316FB979-C146-6A4A-9690-15A0504A98BD}">
+  <dimension ref="B8:J16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="8" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="50"/>
+      <c r="I9" s="50"/>
+      <c r="J9" s="51"/>
+    </row>
+    <row r="10" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="38" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B11" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="45">
+        <v>0.78600000000000003</v>
+      </c>
+      <c r="D11" s="39">
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="E11" s="39">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="F11" s="19">
+        <v>0.82599999999999996</v>
+      </c>
+      <c r="G11" s="39">
+        <v>0.878</v>
+      </c>
+      <c r="H11" s="39">
+        <v>0.83</v>
+      </c>
+      <c r="I11" s="39">
+        <v>0.86299999999999999</v>
+      </c>
+      <c r="J11" s="19">
+        <v>0.88200000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B12" s="47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="41">
+        <v>0.82299999999999995</v>
+      </c>
+      <c r="D12">
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="E12">
+        <v>0.83</v>
+      </c>
+      <c r="F12" s="7">
+        <v>0.86499999999999999</v>
+      </c>
+      <c r="G12">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="H12">
+        <v>0.88300000000000001</v>
+      </c>
+      <c r="I12">
+        <v>0.89900000000000002</v>
+      </c>
+      <c r="J12" s="7">
+        <v>0.90100000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B13" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="41">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="D13">
+        <v>0.73499999999999999</v>
+      </c>
+      <c r="E13">
+        <v>0.76900000000000002</v>
+      </c>
+      <c r="F13" s="7">
+        <v>0.79</v>
+      </c>
+      <c r="G13">
+        <v>0.91800000000000004</v>
+      </c>
+      <c r="H13">
+        <v>0.91400000000000003</v>
+      </c>
+      <c r="I13">
+        <v>0.91800000000000004</v>
+      </c>
+      <c r="J13" s="42">
+        <v>0.91600000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B14" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="41">
+        <v>0.85499999999999998</v>
+      </c>
+      <c r="D14">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="E14">
+        <v>0.88700000000000001</v>
+      </c>
+      <c r="F14" s="7">
+        <v>0.89</v>
+      </c>
+      <c r="G14">
+        <v>0.93899999999999995</v>
+      </c>
+      <c r="H14">
+        <v>0.93600000000000005</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0.95499999999999996</v>
+      </c>
+      <c r="J14" s="42">
+        <v>0.94399999999999995</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B15" s="47" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="41">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="D15">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="E15">
+        <v>0.94899999999999995</v>
+      </c>
+      <c r="F15" s="42">
+        <v>0.94899999999999995</v>
+      </c>
+      <c r="G15">
+        <v>0.99</v>
+      </c>
+      <c r="H15">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="I15">
+        <v>0.99</v>
+      </c>
+      <c r="J15" s="42">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="43">
+        <v>0.80800000000000005</v>
+      </c>
+      <c r="D16" s="44">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="E16" s="44">
+        <v>0.85399999999999998</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.86199999999999999</v>
+      </c>
+      <c r="G16" s="44">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="H16" s="44">
+        <v>0.88400000000000001</v>
+      </c>
+      <c r="I16" s="46">
+        <v>0.92600000000000005</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0.92400000000000004</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14241ACC-8444-A04B-ADDB-6E132B03C7A6}">
+  <dimension ref="B9:F14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="9" spans="2:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+    </row>
+    <row r="10" spans="2:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B11" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="59">
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="D11" s="60">
+        <v>0.89700000000000002</v>
+      </c>
+      <c r="E11" s="60">
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="F11" s="61">
+        <v>0.60099999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B12" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="60">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="D12" s="59">
+        <v>0.36799999999999999</v>
+      </c>
+      <c r="E12" s="60">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="F12" s="61">
+        <v>0.432</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B13" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="59">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="D13" s="60">
+        <v>0.745</v>
+      </c>
+      <c r="E13" s="60">
+        <v>0.40600000000000003</v>
+      </c>
+      <c r="F13" s="61">
+        <v>0.40600000000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="64">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="D14" s="10">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="E14" s="10">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="F14" s="62">
+        <v>0.32900000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFEB83A9-300B-FD43-9873-C4153C381392}">
   <dimension ref="D4:K21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -949,396 +1317,396 @@
       </c>
     </row>
     <row r="6" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D6" s="18">
+      <c r="D6" s="53">
         <v>32</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="19">
         <v>0</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="20">
         <v>0.76873800000000003</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="21">
         <v>0.79974699999999999</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="21">
         <v>0.69001900000000005</v>
       </c>
-      <c r="I6" s="27">
+      <c r="I6" s="21">
         <v>0.81193199999999999</v>
       </c>
-      <c r="J6" s="27">
+      <c r="J6" s="21">
         <v>0.947542</v>
       </c>
-      <c r="K6" s="28">
+      <c r="K6" s="22">
         <v>0.77895099999999995</v>
       </c>
     </row>
     <row r="7" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D7" s="19"/>
+      <c r="D7" s="54"/>
       <c r="E7" s="7">
         <v>0.1</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="23">
         <v>0.77764500000000003</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="24">
         <v>0.80145900000000003</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="24">
         <v>0.684693</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="24">
         <v>0.80647599999999997</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="24">
         <v>0.94765200000000005</v>
       </c>
-      <c r="K7" s="31">
+      <c r="K7" s="25">
         <v>0.78438099999999999</v>
       </c>
     </row>
     <row r="8" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D8" s="19"/>
+      <c r="D8" s="54"/>
       <c r="E8" s="7">
         <v>0.2</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="23">
         <v>0.78338600000000003</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="24">
         <v>0.80404699999999996</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="24">
         <v>0.69981800000000005</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="24">
         <v>0.79473800000000006</v>
       </c>
-      <c r="J8" s="30">
+      <c r="J8" s="24">
         <v>0.94710700000000003</v>
       </c>
-      <c r="K8" s="31">
+      <c r="K8" s="25">
         <v>0.81159400000000004</v>
       </c>
     </row>
     <row r="9" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D9" s="19"/>
+      <c r="D9" s="54"/>
       <c r="E9" s="7">
         <v>0.5</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="23">
         <v>0.78757299999999997</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="24">
         <v>0.81925599999999998</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="24">
         <v>0.69237800000000005</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="24">
         <v>0.70923899999999995</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="24">
         <v>0.94334899999999999</v>
       </c>
-      <c r="K9" s="31">
+      <c r="K9" s="25">
         <v>0.79464500000000005</v>
       </c>
     </row>
     <row r="10" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D10" s="24">
+      <c r="D10" s="55">
         <v>16</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="17">
         <v>0.1</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="26">
         <v>0.77302499999999996</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="27">
         <v>0.78994200000000003</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10" s="27">
         <v>0.68773899999999999</v>
       </c>
-      <c r="I10" s="33">
+      <c r="I10" s="27">
         <v>0.81446600000000002</v>
       </c>
-      <c r="J10" s="33">
+      <c r="J10" s="27">
         <v>0.94726600000000005</v>
       </c>
-      <c r="K10" s="34">
+      <c r="K10" s="28">
         <v>0.79323600000000005</v>
       </c>
     </row>
     <row r="11" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D11" s="19"/>
+      <c r="D11" s="54"/>
       <c r="E11" s="7">
         <v>0.2</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="23">
         <v>0.77680199999999999</v>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="24">
         <v>0.79921399999999998</v>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="29">
         <v>0.702156</v>
       </c>
-      <c r="I11" s="30">
+      <c r="I11" s="24">
         <v>0.787995</v>
       </c>
-      <c r="J11" s="30">
+      <c r="J11" s="24">
         <v>0.946461</v>
       </c>
-      <c r="K11" s="31">
+      <c r="K11" s="25">
         <v>0.801014</v>
       </c>
     </row>
     <row r="12" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D12" s="25"/>
-      <c r="E12" s="22">
+      <c r="D12" s="56"/>
+      <c r="E12" s="18">
         <v>0.5</v>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="30">
         <v>0.785107</v>
       </c>
-      <c r="G12" s="37">
+      <c r="G12" s="31">
         <v>0.81098700000000001</v>
       </c>
-      <c r="H12" s="37">
+      <c r="H12" s="31">
         <v>0.67898899999999995</v>
       </c>
-      <c r="I12" s="37">
+      <c r="I12" s="31">
         <v>0.69854499999999997</v>
       </c>
-      <c r="J12" s="37">
+      <c r="J12" s="31">
         <v>0.94255699999999998</v>
       </c>
-      <c r="K12" s="38">
+      <c r="K12" s="32">
         <v>0.80162299999999997</v>
       </c>
     </row>
     <row r="13" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D13" s="24">
+      <c r="D13" s="55">
         <v>32</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="17">
         <v>0.1</v>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="26">
         <v>0.76945699999999995</v>
       </c>
-      <c r="G13" s="33">
+      <c r="G13" s="27">
         <v>0.81108800000000003</v>
       </c>
-      <c r="H13" s="33">
+      <c r="H13" s="27">
         <v>0.68571599999999999</v>
       </c>
-      <c r="I13" s="33">
+      <c r="I13" s="27">
         <v>0.82045500000000005</v>
       </c>
-      <c r="J13" s="33">
+      <c r="J13" s="27">
         <v>0.94744700000000004</v>
       </c>
-      <c r="K13" s="34">
+      <c r="K13" s="28">
         <v>0.78023799999999999</v>
       </c>
     </row>
     <row r="14" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D14" s="19"/>
+      <c r="D14" s="54"/>
       <c r="E14" s="7">
         <v>0.2</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="23">
         <v>0.77369500000000002</v>
       </c>
-      <c r="G14" s="35">
+      <c r="G14" s="29">
         <v>0.82052599999999998</v>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="24">
         <v>0.68000099999999997</v>
       </c>
-      <c r="I14" s="30">
+      <c r="I14" s="24">
         <v>0.79445600000000005</v>
       </c>
-      <c r="J14" s="30">
+      <c r="J14" s="24">
         <v>0.94710499999999997</v>
       </c>
-      <c r="K14" s="31">
+      <c r="K14" s="25">
         <v>0.81314299999999995</v>
       </c>
     </row>
     <row r="15" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D15" s="25"/>
-      <c r="E15" s="22">
+      <c r="D15" s="56"/>
+      <c r="E15" s="18">
         <v>0.5</v>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="30">
         <v>0.77317999999999998</v>
       </c>
-      <c r="G15" s="37">
+      <c r="G15" s="31">
         <v>0.81305499999999997</v>
       </c>
-      <c r="H15" s="37">
+      <c r="H15" s="31">
         <v>0.68633900000000003</v>
       </c>
-      <c r="I15" s="37">
+      <c r="I15" s="31">
         <v>0.70821100000000003</v>
       </c>
-      <c r="J15" s="37">
+      <c r="J15" s="31">
         <v>0.94359199999999999</v>
       </c>
-      <c r="K15" s="38">
+      <c r="K15" s="32">
         <v>0.80125900000000005</v>
       </c>
     </row>
     <row r="16" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D16" s="24">
+      <c r="D16" s="55">
         <v>64</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="17">
         <v>0.1</v>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="26">
         <v>0.75227200000000005</v>
       </c>
-      <c r="G16" s="33">
+      <c r="G16" s="27">
         <v>0.80803700000000001</v>
       </c>
-      <c r="H16" s="33">
+      <c r="H16" s="27">
         <v>0.69510300000000003</v>
       </c>
-      <c r="I16" s="39">
+      <c r="I16" s="33">
         <v>0.82204500000000003</v>
       </c>
-      <c r="J16" s="39">
+      <c r="J16" s="33">
         <v>0.94786999999999999</v>
       </c>
-      <c r="K16" s="34">
+      <c r="K16" s="28">
         <v>0.78923600000000005</v>
       </c>
     </row>
     <row r="17" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D17" s="19"/>
+      <c r="D17" s="54"/>
       <c r="E17" s="7">
         <v>0.2</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="23">
         <v>0.769509</v>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="24">
         <v>0.813357</v>
       </c>
-      <c r="H17" s="30">
+      <c r="H17" s="24">
         <v>0.67896000000000001</v>
       </c>
-      <c r="I17" s="30">
+      <c r="I17" s="24">
         <v>0.81587100000000001</v>
       </c>
-      <c r="J17" s="30">
+      <c r="J17" s="24">
         <v>0.946326</v>
       </c>
-      <c r="K17" s="31">
+      <c r="K17" s="25">
         <v>0.79243600000000003</v>
       </c>
     </row>
     <row r="18" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D18" s="25"/>
-      <c r="E18" s="22">
+      <c r="D18" s="56"/>
+      <c r="E18" s="18">
         <v>0.5</v>
       </c>
-      <c r="F18" s="40">
+      <c r="F18" s="34">
         <v>0.78776500000000005</v>
       </c>
-      <c r="G18" s="37">
+      <c r="G18" s="31">
         <v>0.81783099999999997</v>
       </c>
-      <c r="H18" s="37">
+      <c r="H18" s="31">
         <v>0.68810700000000002</v>
       </c>
-      <c r="I18" s="37">
+      <c r="I18" s="31">
         <v>0.732792</v>
       </c>
-      <c r="J18" s="37">
+      <c r="J18" s="31">
         <v>0.94385200000000002</v>
       </c>
-      <c r="K18" s="38">
+      <c r="K18" s="32">
         <v>0.81077999999999995</v>
       </c>
     </row>
     <row r="19" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D19" s="19">
+      <c r="D19" s="54">
         <v>128</v>
       </c>
       <c r="E19" s="7">
         <v>0.1</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="23">
         <v>0.78264199999999995</v>
       </c>
-      <c r="G19" s="30">
+      <c r="G19" s="24">
         <v>0.80757699999999999</v>
       </c>
-      <c r="H19" s="30">
+      <c r="H19" s="24">
         <v>0.69794100000000003</v>
       </c>
-      <c r="I19" s="30">
+      <c r="I19" s="24">
         <v>0.801423</v>
       </c>
-      <c r="J19" s="30">
+      <c r="J19" s="24">
         <v>0.94728999999999997</v>
       </c>
-      <c r="K19" s="31">
+      <c r="K19" s="25">
         <v>0.79740500000000003</v>
       </c>
     </row>
     <row r="20" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D20" s="19"/>
+      <c r="D20" s="54"/>
       <c r="E20" s="7">
         <v>0.2</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="23">
         <v>0.76619499999999996</v>
       </c>
-      <c r="G20" s="30">
+      <c r="G20" s="24">
         <v>0.80115199999999998</v>
       </c>
-      <c r="H20" s="30">
+      <c r="H20" s="24">
         <v>0.662053</v>
       </c>
-      <c r="I20" s="30">
+      <c r="I20" s="24">
         <v>0.78976400000000002</v>
       </c>
-      <c r="J20" s="30">
+      <c r="J20" s="24">
         <v>0.94723900000000005</v>
       </c>
-      <c r="K20" s="31">
+      <c r="K20" s="25">
         <v>0.80364599999999997</v>
       </c>
     </row>
     <row r="21" spans="4:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="20"/>
+      <c r="D21" s="57"/>
       <c r="E21" s="3">
         <v>0.5</v>
       </c>
-      <c r="F21" s="41">
+      <c r="F21" s="35">
         <v>0.77475400000000005</v>
       </c>
-      <c r="G21" s="42">
+      <c r="G21" s="36">
         <v>0.81196900000000005</v>
       </c>
-      <c r="H21" s="42">
+      <c r="H21" s="36">
         <v>0.670821</v>
       </c>
-      <c r="I21" s="42">
+      <c r="I21" s="36">
         <v>0.71495500000000001</v>
       </c>
-      <c r="J21" s="42">
+      <c r="J21" s="36">
         <v>0.94326299999999996</v>
       </c>
-      <c r="K21" s="43">
+      <c r="K21" s="37">
         <v>0.81376700000000002</v>
       </c>
     </row>
@@ -1426,7 +1794,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E8A956-A39F-6042-AABD-D2EE41CFE1C2}">
   <dimension ref="C5:G12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/results/Results.xlsx
+++ b/results/Results.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johannes/Documents/GitHub/differentiable-er/results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u0092789\Documents\GitHub\differentiable-er\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9CF6C4-7748-E84A-975D-9943CB36BAC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB7E939-AE0F-4F57-AE2A-EAE971ACC10C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21080" yWindow="9280" windowWidth="23960" windowHeight="17440" activeTab="2" xr2:uid="{A7042B4A-C49B-F340-AB38-2066DB0192FA}"/>
+    <workbookView xWindow="8316" yWindow="1920" windowWidth="24468" windowHeight="18780" activeTab="3" xr2:uid="{A7042B4A-C49B-F340-AB38-2066DB0192FA}"/>
   </bookViews>
   <sheets>
     <sheet name="NAP" sheetId="1" r:id="rId1"/>
     <sheet name="NAP new" sheetId="4" r:id="rId2"/>
     <sheet name="Suffix new" sheetId="5" r:id="rId3"/>
-    <sheet name="NAP detail" sheetId="2" r:id="rId4"/>
-    <sheet name="suffix" sheetId="3" r:id="rId5"/>
+    <sheet name="NAP_with_details_revision" sheetId="6" r:id="rId4"/>
+    <sheet name="NAP detail" sheetId="2" r:id="rId5"/>
+    <sheet name="suffix" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="27">
   <si>
     <t>F1</t>
   </si>
@@ -106,6 +107,21 @@
   </si>
   <si>
     <t>Base</t>
+  </si>
+  <si>
+    <t>DIFF-ERO_local</t>
+  </si>
+  <si>
+    <t>DIFF-ERO_notlocal</t>
+  </si>
+  <si>
+    <t>SDFA_local</t>
+  </si>
+  <si>
+    <t>SDFA_notlocal</t>
+  </si>
+  <si>
+    <t>rank_loss</t>
   </si>
 </sst>
 </file>
@@ -115,7 +131,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -149,13 +165,40 @@
       <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="21">
@@ -388,7 +431,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -441,6 +484,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -459,13 +506,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -801,23 +868,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DD80E6E-625B-C049-8E44-DDAD4AD07F16}">
   <dimension ref="B2:F9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="2" max="2" width="42.5" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C2" s="52" t="s">
+    <row r="2" spans="2:6">
+      <c r="C2" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52" t="s">
+      <c r="D2" s="56"/>
+      <c r="E2" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="52"/>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F2" s="56"/>
+    </row>
+    <row r="3" spans="2:6">
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
@@ -834,7 +901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:6">
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
@@ -851,7 +918,7 @@
         <v>0.877</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:6">
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
@@ -868,7 +935,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:6">
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
@@ -885,7 +952,7 @@
         <v>0.90800000000000003</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:6">
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -902,7 +969,7 @@
         <v>0.94399999999999995</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:6">
       <c r="B8" t="s">
         <v>9</v>
       </c>
@@ -919,7 +986,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:6">
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
@@ -948,13 +1015,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{316FB979-C146-6A4A-9690-15A0504A98BD}">
   <dimension ref="B8:J16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="8" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" ht="16.2" thickBot="1"/>
+    <row r="9" spans="2:10" ht="16.2" thickBot="1">
       <c r="C9" s="38" t="s">
         <v>0</v>
       </c>
@@ -968,7 +1035,7 @@
       <c r="I9" s="50"/>
       <c r="J9" s="51"/>
     </row>
-    <row r="10" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" ht="16.2" thickBot="1">
       <c r="B10" s="38" t="s">
         <v>4</v>
       </c>
@@ -997,7 +1064,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:10">
       <c r="B11" s="38" t="s">
         <v>5</v>
       </c>
@@ -1026,7 +1093,7 @@
         <v>0.88200000000000001</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:10">
       <c r="B12" s="47" t="s">
         <v>6</v>
       </c>
@@ -1055,7 +1122,7 @@
         <v>0.90100000000000002</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:10">
       <c r="B13" s="47" t="s">
         <v>7</v>
       </c>
@@ -1084,7 +1151,7 @@
         <v>0.91600000000000004</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:10">
       <c r="B14" s="47" t="s">
         <v>12</v>
       </c>
@@ -1113,7 +1180,7 @@
         <v>0.94399999999999995</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:10">
       <c r="B15" s="47" t="s">
         <v>13</v>
       </c>
@@ -1142,7 +1209,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="16" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" ht="16.2" thickBot="1">
       <c r="B16" s="48" t="s">
         <v>14</v>
       </c>
@@ -1179,20 +1246,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14241ACC-8444-A04B-ADDB-6E132B03C7A6}">
   <dimension ref="B9:F14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="58"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-    </row>
-    <row r="10" spans="2:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="63" t="s">
+    <row r="9" spans="2:6" ht="16.2" thickBot="1"/>
+    <row r="10" spans="2:6" ht="16.2" thickBot="1">
+      <c r="B10" s="54" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="5" t="s">
@@ -1208,62 +1269,62 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:6">
       <c r="B11" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="59">
+      <c r="C11" s="8">
         <v>0.56699999999999995</v>
       </c>
-      <c r="D11" s="60">
+      <c r="D11" s="9">
         <v>0.89700000000000002</v>
       </c>
-      <c r="E11" s="60">
+      <c r="E11" s="9">
         <v>0.59899999999999998</v>
       </c>
-      <c r="F11" s="61">
+      <c r="F11" s="52">
         <v>0.60099999999999998</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:6">
       <c r="B12" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="60">
+      <c r="C12" s="9">
         <v>0.40500000000000003</v>
       </c>
-      <c r="D12" s="59">
+      <c r="D12" s="8">
         <v>0.36799999999999999</v>
       </c>
-      <c r="E12" s="60">
+      <c r="E12" s="9">
         <v>0.42499999999999999</v>
       </c>
-      <c r="F12" s="61">
+      <c r="F12" s="52">
         <v>0.432</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:6">
       <c r="B13" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="59">
+      <c r="C13" s="8">
         <v>0.38200000000000001</v>
       </c>
-      <c r="D13" s="60">
+      <c r="D13" s="9">
         <v>0.745</v>
       </c>
-      <c r="E13" s="60">
+      <c r="E13" s="9">
         <v>0.40600000000000003</v>
       </c>
-      <c r="F13" s="61">
+      <c r="F13" s="52">
         <v>0.40600000000000003</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" ht="16.2" thickBot="1">
       <c r="B14" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="64">
+      <c r="C14" s="55">
         <v>0.32100000000000001</v>
       </c>
       <c r="D14" s="10">
@@ -1272,7 +1333,7 @@
       <c r="E14" s="10">
         <v>0.33400000000000002</v>
       </c>
-      <c r="F14" s="62">
+      <c r="F14" s="53">
         <v>0.32900000000000001</v>
       </c>
     </row>
@@ -1282,15 +1343,400 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{399B76F9-9AD7-4194-B24E-05B62642BBFB}">
+  <dimension ref="A5:Q14"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="3" max="3" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.19921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="1:17" ht="16.2" thickBot="1">
+      <c r="A5" s="63"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="63"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="63"/>
+    </row>
+    <row r="6" spans="1:17" ht="15.6" customHeight="1" thickBot="1">
+      <c r="A6" s="63"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="64" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="66"/>
+      <c r="O6" s="63"/>
+      <c r="Q6" s="62"/>
+    </row>
+    <row r="7" spans="1:17" ht="16.2" thickBot="1">
+      <c r="A7" s="63"/>
+      <c r="B7" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="69" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" s="69" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" s="63"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="63"/>
+      <c r="B8" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="71">
+        <v>0.78600000000000003</v>
+      </c>
+      <c r="D8" s="72">
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="E8" s="72">
+        <v>0.71399999999999997</v>
+      </c>
+      <c r="F8" s="72">
+        <v>0.66600000000000004</v>
+      </c>
+      <c r="G8" s="73">
+        <v>0.81899999999999995</v>
+      </c>
+      <c r="H8" s="74">
+        <v>0.81</v>
+      </c>
+      <c r="I8" s="71">
+        <v>0.878</v>
+      </c>
+      <c r="J8" s="72">
+        <v>0.83</v>
+      </c>
+      <c r="K8" s="72">
+        <v>0.86599999999999999</v>
+      </c>
+      <c r="L8" s="72">
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="M8" s="72">
+        <v>0.877</v>
+      </c>
+      <c r="N8" s="75">
+        <v>0.88200000000000001</v>
+      </c>
+      <c r="O8" s="63"/>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="63"/>
+      <c r="B9" s="70" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="71">
+        <v>0.82299999999999995</v>
+      </c>
+      <c r="D9" s="72">
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="E9" s="72">
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="F9" s="72">
+        <v>0.79800000000000004</v>
+      </c>
+      <c r="G9" s="73">
+        <v>0.86299999999999999</v>
+      </c>
+      <c r="H9" s="74">
+        <v>0.84099999999999997</v>
+      </c>
+      <c r="I9" s="71">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="J9" s="72">
+        <v>0.88300000000000001</v>
+      </c>
+      <c r="K9" s="73">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="L9" s="72">
+        <v>0.89400000000000002</v>
+      </c>
+      <c r="M9" s="72">
+        <v>0.9</v>
+      </c>
+      <c r="N9" s="74">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="O9" s="63"/>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="63"/>
+      <c r="B10" s="70" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="71">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="D10" s="72">
+        <v>0.73499999999999999</v>
+      </c>
+      <c r="E10" s="72">
+        <v>0.751</v>
+      </c>
+      <c r="F10" s="72">
+        <v>0.73799999999999999</v>
+      </c>
+      <c r="G10" s="73">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="H10" s="74">
+        <v>0.755</v>
+      </c>
+      <c r="I10" s="70">
+        <v>0.91800000000000004</v>
+      </c>
+      <c r="J10" s="72">
+        <v>0.91400000000000003</v>
+      </c>
+      <c r="K10" s="72">
+        <v>0.91300000000000003</v>
+      </c>
+      <c r="L10" s="72">
+        <v>0.91400000000000003</v>
+      </c>
+      <c r="M10" s="72">
+        <v>0.91</v>
+      </c>
+      <c r="N10" s="74">
+        <v>0.91300000000000003</v>
+      </c>
+      <c r="O10" s="63"/>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="63"/>
+      <c r="B11" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="71">
+        <v>0.85499999999999998</v>
+      </c>
+      <c r="D11" s="72">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="E11" s="72">
+        <v>0.88600000000000001</v>
+      </c>
+      <c r="F11" s="72">
+        <v>0.874</v>
+      </c>
+      <c r="G11" s="73">
+        <v>0.89</v>
+      </c>
+      <c r="H11" s="74">
+        <v>0.85099999999999998</v>
+      </c>
+      <c r="I11" s="71">
+        <v>0.93899999999999995</v>
+      </c>
+      <c r="J11" s="72">
+        <v>0.93600000000000005</v>
+      </c>
+      <c r="K11" s="73">
+        <v>0.95499999999999996</v>
+      </c>
+      <c r="L11" s="73">
+        <v>0.95499999999999996</v>
+      </c>
+      <c r="M11" s="72">
+        <v>0.94499999999999995</v>
+      </c>
+      <c r="N11" s="74">
+        <v>0.94399999999999995</v>
+      </c>
+      <c r="O11" s="63"/>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="63"/>
+      <c r="B12" s="70" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="71">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="D12" s="72">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="E12" s="72">
+        <v>0.94899999999999995</v>
+      </c>
+      <c r="F12" s="72">
+        <v>0.94899999999999995</v>
+      </c>
+      <c r="G12" s="72">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="H12" s="74">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="I12" s="71">
+        <v>0.99</v>
+      </c>
+      <c r="J12" s="72">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="K12" s="72">
+        <v>0.99</v>
+      </c>
+      <c r="L12" s="72">
+        <v>0.99</v>
+      </c>
+      <c r="M12" s="72">
+        <v>0.99</v>
+      </c>
+      <c r="N12" s="74">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="O12" s="63"/>
+    </row>
+    <row r="13" spans="1:17" ht="16.2" thickBot="1">
+      <c r="A13" s="63"/>
+      <c r="B13" s="76" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="77">
+        <v>0.80800000000000005</v>
+      </c>
+      <c r="D13" s="78">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="E13" s="78">
+        <v>0.85299999999999998</v>
+      </c>
+      <c r="F13" s="78">
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="G13" s="79">
+        <v>0.86</v>
+      </c>
+      <c r="H13" s="80">
+        <v>0.84499999999999997</v>
+      </c>
+      <c r="I13" s="77">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="J13" s="78">
+        <v>0.88400000000000001</v>
+      </c>
+      <c r="K13" s="78">
+        <v>0.92600000000000005</v>
+      </c>
+      <c r="L13" s="78">
+        <v>0.90800000000000003</v>
+      </c>
+      <c r="M13" s="79">
+        <v>0.92300000000000004</v>
+      </c>
+      <c r="N13" s="80">
+        <v>0.92100000000000004</v>
+      </c>
+      <c r="O13" s="63"/>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="63"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="63"/>
+      <c r="K14" s="63"/>
+      <c r="L14" s="63"/>
+      <c r="M14" s="63"/>
+      <c r="N14" s="63"/>
+      <c r="O14" s="63"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="I6:N6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFEB83A9-300B-FD43-9873-C4153C381392}">
   <dimension ref="D4:K21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="4" max="4" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="4:11" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="4:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="4:11" ht="16.2" thickBot="1"/>
+    <row r="5" spans="4:11" ht="16.2" thickBot="1">
       <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
@@ -1316,8 +1762,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D6" s="53">
+    <row r="6" spans="4:11">
+      <c r="D6" s="57">
         <v>32</v>
       </c>
       <c r="E6" s="19">
@@ -1342,8 +1788,8 @@
         <v>0.77895099999999995</v>
       </c>
     </row>
-    <row r="7" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D7" s="54"/>
+    <row r="7" spans="4:11">
+      <c r="D7" s="58"/>
       <c r="E7" s="7">
         <v>0.1</v>
       </c>
@@ -1366,8 +1812,8 @@
         <v>0.78438099999999999</v>
       </c>
     </row>
-    <row r="8" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D8" s="54"/>
+    <row r="8" spans="4:11">
+      <c r="D8" s="58"/>
       <c r="E8" s="7">
         <v>0.2</v>
       </c>
@@ -1390,8 +1836,8 @@
         <v>0.81159400000000004</v>
       </c>
     </row>
-    <row r="9" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D9" s="54"/>
+    <row r="9" spans="4:11">
+      <c r="D9" s="58"/>
       <c r="E9" s="7">
         <v>0.5</v>
       </c>
@@ -1414,8 +1860,8 @@
         <v>0.79464500000000005</v>
       </c>
     </row>
-    <row r="10" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D10" s="55">
+    <row r="10" spans="4:11">
+      <c r="D10" s="59">
         <v>16</v>
       </c>
       <c r="E10" s="17">
@@ -1440,8 +1886,8 @@
         <v>0.79323600000000005</v>
       </c>
     </row>
-    <row r="11" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D11" s="54"/>
+    <row r="11" spans="4:11">
+      <c r="D11" s="58"/>
       <c r="E11" s="7">
         <v>0.2</v>
       </c>
@@ -1464,8 +1910,8 @@
         <v>0.801014</v>
       </c>
     </row>
-    <row r="12" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D12" s="56"/>
+    <row r="12" spans="4:11">
+      <c r="D12" s="60"/>
       <c r="E12" s="18">
         <v>0.5</v>
       </c>
@@ -1488,8 +1934,8 @@
         <v>0.80162299999999997</v>
       </c>
     </row>
-    <row r="13" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D13" s="55">
+    <row r="13" spans="4:11">
+      <c r="D13" s="59">
         <v>32</v>
       </c>
       <c r="E13" s="17">
@@ -1514,8 +1960,8 @@
         <v>0.78023799999999999</v>
       </c>
     </row>
-    <row r="14" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D14" s="54"/>
+    <row r="14" spans="4:11">
+      <c r="D14" s="58"/>
       <c r="E14" s="7">
         <v>0.2</v>
       </c>
@@ -1538,8 +1984,8 @@
         <v>0.81314299999999995</v>
       </c>
     </row>
-    <row r="15" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D15" s="56"/>
+    <row r="15" spans="4:11">
+      <c r="D15" s="60"/>
       <c r="E15" s="18">
         <v>0.5</v>
       </c>
@@ -1562,8 +2008,8 @@
         <v>0.80125900000000005</v>
       </c>
     </row>
-    <row r="16" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D16" s="55">
+    <row r="16" spans="4:11">
+      <c r="D16" s="59">
         <v>64</v>
       </c>
       <c r="E16" s="17">
@@ -1588,8 +2034,8 @@
         <v>0.78923600000000005</v>
       </c>
     </row>
-    <row r="17" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D17" s="54"/>
+    <row r="17" spans="4:11">
+      <c r="D17" s="58"/>
       <c r="E17" s="7">
         <v>0.2</v>
       </c>
@@ -1612,8 +2058,8 @@
         <v>0.79243600000000003</v>
       </c>
     </row>
-    <row r="18" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D18" s="56"/>
+    <row r="18" spans="4:11">
+      <c r="D18" s="60"/>
       <c r="E18" s="18">
         <v>0.5</v>
       </c>
@@ -1636,8 +2082,8 @@
         <v>0.81077999999999995</v>
       </c>
     </row>
-    <row r="19" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D19" s="54">
+    <row r="19" spans="4:11">
+      <c r="D19" s="58">
         <v>128</v>
       </c>
       <c r="E19" s="7">
@@ -1662,8 +2108,8 @@
         <v>0.79740500000000003</v>
       </c>
     </row>
-    <row r="20" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D20" s="54"/>
+    <row r="20" spans="4:11">
+      <c r="D20" s="58"/>
       <c r="E20" s="7">
         <v>0.2</v>
       </c>
@@ -1686,8 +2132,8 @@
         <v>0.80364599999999997</v>
       </c>
     </row>
-    <row r="21" spans="4:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="57"/>
+    <row r="21" spans="4:11" ht="16.2" thickBot="1">
+      <c r="D21" s="61"/>
       <c r="E21" s="3">
         <v>0.5</v>
       </c>
@@ -1794,16 +2240,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E8A956-A39F-6042-AABD-D2EE41CFE1C2}">
   <dimension ref="C5:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:7" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="3:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:7" ht="16.2" thickBot="1"/>
+    <row r="6" spans="3:7" ht="16.2" thickBot="1">
       <c r="C6" s="13" t="s">
         <v>4</v>
       </c>
@@ -1818,7 +2264,7 @@
       </c>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="3:7">
       <c r="C7" s="11" t="s">
         <v>5</v>
       </c>
@@ -1833,7 +2279,7 @@
       </c>
       <c r="G7" s="9"/>
     </row>
-    <row r="8" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="3:7">
       <c r="C8" s="11" t="s">
         <v>6</v>
       </c>
@@ -1848,7 +2294,7 @@
       </c>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="3:7">
       <c r="C9" s="11" t="s">
         <v>7</v>
       </c>
@@ -1863,7 +2309,7 @@
       </c>
       <c r="G9" s="9"/>
     </row>
-    <row r="10" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="3:7">
       <c r="C10" s="11" t="s">
         <v>12</v>
       </c>
@@ -1878,7 +2324,7 @@
       </c>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="3:7">
       <c r="C11" s="11" t="s">
         <v>13</v>
       </c>
@@ -1893,7 +2339,7 @@
       </c>
       <c r="G11" s="9"/>
     </row>
-    <row r="12" spans="3:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:7" ht="16.2" thickBot="1">
       <c r="C12" s="12" t="s">
         <v>14</v>
       </c>
